--- a/vdi-ops/reports/VDI_월간점검보고서_초안_2026-05.xlsx
+++ b/vdi-ops/reports/VDI_월간점검보고서_초안_2026-05.xlsx
@@ -107,9 +107,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0">
       <alignment vertical="center" wrapText="1"/>
